--- a/baseline_models/ijkdijk_runs.xlsx
+++ b/baseline_models/ijkdijk_runs.xlsx
@@ -509,22 +509,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,55 +541,60 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>layer_s1</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>active_model</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>gamma_dry</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>gamma_wet</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Su_S</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Su_m</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>MC_phi</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>MC_c</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>MC_psi</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>su_table_key</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Layers</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>POP</t>
         </is>
@@ -607,19 +613,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>L 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>19</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>20</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>37.56</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,19 +647,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>L 9, L 7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>15.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>19.5</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>31.49</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -665,19 +681,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>L 8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>MohrCoulombClassic</t>
         </is>
-      </c>
-      <c r="D4" t="n">
-        <v>15.75</v>
       </c>
       <c r="E4" t="n">
         <v>15.75</v>
       </c>
-      <c r="H4" t="n">
+      <c r="F4" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -694,29 +715,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>L 2, L 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.5</v>
       </c>
       <c r="E5" t="n">
         <v>10.5</v>
       </c>
       <c r="F5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.76</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.8</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SP 1, SP 2</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1, 0.1</t>
+          <t>SP 1, SP 2, SP 8</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.1, 0.1, 0.1</t>
         </is>
       </c>
     </row>
@@ -733,29 +759,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>L 3, L 6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
-      </c>
-      <c r="D6" t="n">
-        <v>15.9</v>
       </c>
       <c r="E6" t="n">
         <v>15.9</v>
       </c>
       <c r="F6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.38</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.8</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SP 3, SP 4</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.1, 0.1</t>
+          <t>SP 3, SP 4, SP 6</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.1, 0.1, 0.1</t>
         </is>
       </c>
     </row>
@@ -772,29 +803,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>L 5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Su</t>
         </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.5</v>
       </c>
       <c r="E7" t="n">
         <v>10.5</v>
       </c>
       <c r="F7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.76</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.8</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SP 5</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>SP 5, SP 7</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.1, 0.1</t>
         </is>
       </c>
     </row>

--- a/baseline_models/ijkdijk_runs.xlsx
+++ b/baseline_models/ijkdijk_runs.xlsx
@@ -514,7 +514,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L 9, L 7</t>
+          <t>L 12, L 10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L 2, L 4</t>
+          <t>L 2, L 4, L 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L 3, L 6</t>
+          <t>L 7, L 9, L 8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6, L 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/baseline_models/ijkdijk_runs.xlsx
+++ b/baseline_models/ijkdijk_runs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-6030" windowWidth="16440" windowHeight="28320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3900" yWindow="345" windowWidth="12150" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" state="visible" r:id="rId1"/>
@@ -24334,17 +24334,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:39</t>
+          <t>2026-05-28 12:22:00</t>
         </is>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9325822812343554</v>
+        <v>0.9313674276604081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9148843133712994</v>
+        <v>0.9183226402690196</v>
       </c>
     </row>
     <row r="3">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:47</t>
+          <t>2026-05-28 12:22:10</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -24386,17 +24386,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-18 11:21:52</t>
+          <t>2026-05-28 12:22:17</t>
         </is>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9350042378239427</v>
+        <v>0.9357644555891874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9219648198530366</v>
+        <v>0.924240939408446</v>
       </c>
     </row>
     <row r="5">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:01</t>
+          <t>2026-05-28 12:22:28</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -24438,17 +24438,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:06</t>
+          <t>2026-05-28 12:22:36</t>
         </is>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8998731233597227</v>
+        <v>0.8978679483764915</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8661467794338811</v>
+        <v>0.8773386916253549</v>
       </c>
     </row>
     <row r="7">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:14</t>
+          <t>2026-05-28 12:22:45</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:20</t>
+          <t>2026-05-28 12:22:53</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:28</t>
+          <t>2026-05-28 12:23:04</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:34</t>
+          <t>2026-05-28 12:23:12</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:43</t>
+          <t>2026-05-28 12:23:22</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:49</t>
+          <t>2026-05-28 12:23:30</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-18 11:22:56</t>
+          <t>2026-05-28 12:23:40</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:02</t>
+          <t>2026-05-28 12:23:47</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -24672,7 +24672,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:10</t>
+          <t>2026-05-28 12:23:57</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -24698,17 +24698,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:15</t>
+          <t>2026-05-28 12:24:03</t>
         </is>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6403037579890204</v>
+        <v>0.6447473434995034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7122298601713494</v>
+        <v>0.7294068029095861</v>
       </c>
     </row>
     <row r="17">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:23</t>
+          <t>2026-05-28 12:24:12</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -24750,17 +24750,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:28</t>
+          <t>2026-05-28 12:24:18</t>
         </is>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6550446804526652</v>
+        <v>0.6594533356492267</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7293647578074972</v>
+        <v>0.7455307007834006</v>
       </c>
     </row>
     <row r="19">
@@ -24776,7 +24776,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:35</t>
+          <t>2026-05-28 12:24:28</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -24802,17 +24802,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:41</t>
+          <t>2026-05-28 12:24:35</t>
         </is>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6438296983635089</v>
+        <v>0.6480582035145244</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7184919499054695</v>
+        <v>0.7362154980937871</v>
       </c>
     </row>
     <row r="21">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:48</t>
+          <t>2026-05-28 12:24:45</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -24854,17 +24854,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-18 11:23:53</t>
+          <t>2026-05-28 12:24:51</t>
         </is>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6586455340194017</v>
+        <v>0.663092822627384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7357009694074799</v>
+        <v>0.752406821079271</v>
       </c>
     </row>
     <row r="23">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:01</t>
+          <t>2026-05-28 12:25:01</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -24906,17 +24906,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:06</t>
+          <t>2026-05-28 12:25:08</t>
         </is>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6221609017911137</v>
+        <v>0.6246851185848359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6691906679578788</v>
+        <v>0.6827549715591454</v>
       </c>
     </row>
     <row r="25">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:14</t>
+          <t>2026-05-28 12:25:17</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -24958,17 +24958,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:19</t>
+          <t>2026-05-28 12:25:24</t>
         </is>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6297485169545558</v>
+        <v>0.6338984094320581</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6858092360954245</v>
+        <v>0.6984083643629335</v>
       </c>
     </row>
     <row r="27">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:27</t>
+          <t>2026-05-28 12:25:33</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -25010,17 +25010,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:32</t>
+          <t>2026-05-28 12:25:39</t>
         </is>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6863829103878754</v>
+        <v>0.7040692320842973</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6676385209676928</v>
+        <v>0.7022841612597917</v>
       </c>
     </row>
     <row r="29">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:40</t>
+          <t>2026-05-28 12:25:48</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -25062,17 +25062,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:45</t>
+          <t>2026-05-28 12:25:55</t>
         </is>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6953574954094793</v>
+        <v>0.7126660139940455</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6687742341674274</v>
+        <v>0.7099618107091675</v>
       </c>
     </row>
     <row r="31">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:52</t>
+          <t>2026-05-28 12:26:04</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -25114,17 +25114,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05-18 11:24:58</t>
+          <t>2026-05-28 12:26:10</t>
         </is>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.690506576698958</v>
+        <v>0.7080025395719465</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6736901375370803</v>
+        <v>0.7076258936695208</v>
       </c>
     </row>
     <row r="33">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:05</t>
+          <t>2026-05-28 12:26:19</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -25166,17 +25166,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:10</t>
+          <t>2026-05-28 12:26:26</t>
         </is>
       </c>
       <c r="D34" t="b">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.699519515729767</v>
+        <v>0.7166346468420913</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6748310588736152</v>
+        <v>0.7153372868452239</v>
       </c>
     </row>
     <row r="35">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:18</t>
+          <t>2026-05-28 12:26:35</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -25218,17 +25218,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:24</t>
+          <t>2026-05-28 12:26:42</t>
         </is>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6575758102713777</v>
+        <v>0.6766917202969444</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6260653615217985</v>
+        <v>0.6476971618162031</v>
       </c>
     </row>
     <row r="37">
@@ -25244,7 +25244,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:32</t>
+          <t>2026-05-28 12:26:51</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -25270,17 +25270,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:38</t>
+          <t>2026-05-28 12:26:58</t>
         </is>
       </c>
       <c r="D38" t="b">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.666274847768749</v>
+        <v>0.6850578252280251</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6271647454562401</v>
+        <v>0.6491002486137135</v>
       </c>
     </row>
     <row r="39">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:45</t>
+          <t>2026-05-28 12:27:07</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -25322,14 +25322,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-05-18 11:25:51</t>
+          <t>2026-05-28 12:27:15</t>
         </is>
       </c>
       <c r="D40" t="b">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9634979156344996</v>
+        <v>0.9715996269709197</v>
       </c>
       <c r="F40" t="n">
         <v>0.9463063133842711</v>
@@ -25348,7 +25348,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:00</t>
+          <t>2026-05-28 12:27:26</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -25374,14 +25374,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:06</t>
+          <t>2026-05-28 12:27:33</t>
         </is>
       </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9706241337600687</v>
+        <v>0.9779997926075252</v>
       </c>
       <c r="F42" t="n">
         <v>0.9501714158621705</v>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:15</t>
+          <t>2026-05-28 12:27:44</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -25426,14 +25426,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:21</t>
+          <t>2026-05-28 12:27:51</t>
         </is>
       </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9990842032721466</v>
+        <v>1.007245628347618</v>
       </c>
       <c r="F44" t="n">
         <v>0.9859600797022288</v>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:30</t>
+          <t>2026-05-28 12:28:02</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -25478,14 +25478,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:36</t>
+          <t>2026-05-28 12:28:09</t>
         </is>
       </c>
       <c r="D46" t="b">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1.006210421397716</v>
+        <v>1.013645847319352</v>
       </c>
       <c r="F46" t="n">
         <v>0.9898252237348545</v>
@@ -25504,7 +25504,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:51</t>
+          <t>2026-05-28 12:28:26</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -25530,14 +25530,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-18 11:26:57</t>
+          <t>2026-05-28 12:28:33</t>
         </is>
       </c>
       <c r="D48" t="b">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1.216228619392338</v>
+        <v>1.241851271974181</v>
       </c>
       <c r="F48" t="n">
         <v>1.224218905820375</v>
@@ -25556,7 +25556,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:05</t>
+          <t>2026-05-28 12:28:42</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -25582,14 +25582,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:11</t>
+          <t>2026-05-28 12:28:50</t>
         </is>
       </c>
       <c r="D50" t="b">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.223354837517907</v>
+        <v>1.24841538600271</v>
       </c>
       <c r="F50" t="n">
         <v>1.228084219489427</v>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:19</t>
+          <t>2026-05-28 12:29:00</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -25634,14 +25634,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:25</t>
+          <t>2026-05-28 12:29:07</t>
         </is>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1.266978745533372</v>
+        <v>1.292882344575017</v>
       </c>
       <c r="F52" t="n">
         <v>1.280549981953451</v>
@@ -25660,7 +25660,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:40</t>
+          <t>2026-05-28 12:29:25</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -25686,14 +25686,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:46</t>
+          <t>2026-05-28 12:29:32</t>
         </is>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1.274104963658941</v>
+        <v>1.299446474164108</v>
       </c>
       <c r="F54" t="n">
         <v>1.284415322404287</v>
@@ -25712,7 +25712,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-18 11:27:54</t>
+          <t>2026-05-28 12:29:43</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -25738,17 +25738,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:04</t>
+          <t>2026-05-28 12:29:50</t>
         </is>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7511428954715287</v>
+        <v>0.7484425910310099</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7583296649339265</v>
+        <v>0.7778731761682889</v>
       </c>
     </row>
     <row r="57">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:18</t>
+          <t>2026-05-28 12:30:06</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -25790,17 +25790,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:24</t>
+          <t>2026-05-28 12:30:12</t>
         </is>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7664270050907541</v>
+        <v>0.7695323724817863</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7770935040284003</v>
+        <v>0.796128366142852</v>
       </c>
     </row>
     <row r="59">
@@ -25816,7 +25816,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:33</t>
+          <t>2026-05-28 12:30:22</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -25842,17 +25842,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:38</t>
+          <t>2026-05-28 12:30:29</t>
         </is>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7494509367667642</v>
+        <v>0.7525358107491352</v>
       </c>
       <c r="F60" t="n">
-        <v>0.764789296814372</v>
+        <v>0.7848824621700692</v>
       </c>
     </row>
     <row r="61">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:48</t>
+          <t>2026-05-28 12:30:41</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -25894,17 +25894,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-05-18 11:28:53</t>
+          <t>2026-05-28 12:30:47</t>
         </is>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7705070143716418</v>
+        <v>0.7737133703519815</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7836318026772032</v>
+        <v>0.8032115544804324</v>
       </c>
     </row>
     <row r="63">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:01</t>
+          <t>2026-05-28 12:30:56</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -25946,17 +25946,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:11</t>
+          <t>2026-05-28 12:31:03</t>
         </is>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7226469237713684</v>
+        <v>0.719764184314919</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7139154843809169</v>
+        <v>0.7298228927479042</v>
       </c>
     </row>
     <row r="65">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:18</t>
+          <t>2026-05-28 12:31:12</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -25998,17 +25998,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:23</t>
+          <t>2026-05-28 12:31:19</t>
         </is>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7379486470921308</v>
+        <v>0.7402518491872198</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7321327011711236</v>
+        <v>0.7475638244538184</v>
       </c>
     </row>
     <row r="67">
@@ -26024,7 +26024,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:31</t>
+          <t>2026-05-28 12:31:28</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -26050,7 +26050,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:37</t>
+          <t>2026-05-28 12:31:34</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:45</t>
+          <t>2026-05-28 12:31:44</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:50</t>
+          <t>2026-05-28 12:31:51</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-05-18 11:29:58</t>
+          <t>2026-05-28 12:32:01</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:04</t>
+          <t>2026-05-28 12:32:08</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:12</t>
+          <t>2026-05-28 12:32:18</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:17</t>
+          <t>2026-05-28 12:32:25</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:26</t>
+          <t>2026-05-28 12:32:35</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:32</t>
+          <t>2026-05-28 12:32:41</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:39</t>
+          <t>2026-05-28 12:32:51</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:46</t>
+          <t>2026-05-28 12:32:58</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-05-18 11:30:54</t>
+          <t>2026-05-28 12:33:09</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-05-18 11:31:00</t>
+          <t>2026-05-28 12:33:16</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -26388,7 +26388,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-05-18 11:31:09</t>
+          <t>2026-05-28 12:33:26</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-05-18 11:31:14</t>
+          <t>2026-05-28 12:33:33</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-05-18 11:31:23</t>
+          <t>2026-05-28 12:33:43</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -26466,17 +26466,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-05-27 16:26:55</t>
+          <t>2026-05-28 12:33:55</t>
         </is>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.739998509240903</v>
+        <v>0.739748208041207</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7471435237228767</v>
+        <v>0.7672321216330761</v>
       </c>
     </row>
     <row r="85">
@@ -26492,7 +26492,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:07</t>
+          <t>2026-05-28 12:34:10</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -26518,17 +26518,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:14</t>
+          <t>2026-05-28 12:34:19</t>
         </is>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7505333127426631</v>
+        <v>0.7581121699476271</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7641216172768788</v>
+        <v>0.7838266376249012</v>
       </c>
     </row>
     <row r="87">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:22</t>
+          <t>2026-05-28 12:34:28</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -26570,17 +26570,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:32</t>
+          <t>2026-05-28 12:34:40</t>
         </is>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7440191772409295</v>
+        <v>0.743808911448973</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7535557743388471</v>
+        <v>0.7741979065568481</v>
       </c>
     </row>
     <row r="89">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:44</t>
+          <t>2026-05-28 12:34:55</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -26622,17 +26622,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-05-27 16:27:50</t>
+          <t>2026-05-28 12:35:02</t>
         </is>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7545066346460462</v>
+        <v>0.7622486932516287</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7706056406546642</v>
+        <v>0.790860126218396</v>
       </c>
     </row>
     <row r="91">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:04</t>
+          <t>2026-05-28 12:35:19</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -26674,17 +26674,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:18</t>
+          <t>2026-05-28 12:35:31</t>
         </is>
       </c>
       <c r="D92" t="b">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7116172373403837</v>
+        <v>0.7112986599604337</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7030588275075611</v>
+        <v>0.7194847828923929</v>
       </c>
     </row>
     <row r="93">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:26</t>
+          <t>2026-05-28 12:35:41</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -26726,17 +26726,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:37</t>
+          <t>2026-05-28 12:35:48</t>
         </is>
       </c>
       <c r="D94" t="b">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7325121644113913</v>
+        <v>0.7293092035909696</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7195378951905916</v>
+        <v>0.7356078822297355</v>
       </c>
     </row>
     <row r="95">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:46</t>
+          <t>2026-05-28 12:35:58</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-05-27 16:28:53</t>
+          <t>2026-05-28 12:36:05</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:01</t>
+          <t>2026-05-28 12:36:14</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:08</t>
+          <t>2026-05-28 12:36:24</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:16</t>
+          <t>2026-05-28 12:36:35</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -26882,7 +26882,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:23</t>
+          <t>2026-05-28 12:36:43</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:31</t>
+          <t>2026-05-28 12:36:55</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:37</t>
+          <t>2026-05-28 12:37:03</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:46</t>
+          <t>2026-05-28 12:37:13</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -26986,14 +26986,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-27 16:29:52</t>
+          <t>2026-05-28 12:37:21</t>
         </is>
       </c>
       <c r="D104" t="b">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>1.228888953771692</v>
+        <v>1.268674390646135</v>
       </c>
       <c r="F104" t="n">
         <v>1.265653427671221</v>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:00</t>
+          <t>2026-05-28 12:37:30</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:07</t>
+          <t>2026-05-28 12:37:38</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:15</t>
+          <t>2026-05-28 12:37:49</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -27090,14 +27090,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:22</t>
+          <t>2026-05-28 12:37:56</t>
         </is>
       </c>
       <c r="D108" t="b">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>1.281642248649183</v>
+        <v>1.319491464490042</v>
       </c>
       <c r="F108" t="n">
         <v>1.312891507320068</v>
@@ -27116,7 +27116,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:30</t>
+          <t>2026-05-28 12:38:06</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:38</t>
+          <t>2026-05-28 12:38:17</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:46</t>
+          <t>2026-05-28 12:38:28</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -27194,17 +27194,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-05-27 16:30:56</t>
+          <t>2026-05-28 12:38:35</t>
         </is>
       </c>
       <c r="D112" t="b">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7236114633033076</v>
+        <v>0.7177673050417738</v>
       </c>
       <c r="F112" t="n">
-        <v>0.734559944917457</v>
+        <v>0.7549455776854284</v>
       </c>
     </row>
     <row r="113">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:07</t>
+          <t>2026-05-28 12:38:48</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -27246,17 +27246,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:16</t>
+          <t>2026-05-28 12:38:55</t>
         </is>
       </c>
       <c r="D114" t="b">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7437186663764183</v>
+        <v>0.7412066977460062</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7501806398172362</v>
+        <v>0.7702574155321058</v>
       </c>
     </row>
     <row r="115">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:30</t>
+          <t>2026-05-28 12:39:12</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -27298,17 +27298,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:39</t>
+          <t>2026-05-28 12:39:19</t>
         </is>
       </c>
       <c r="D116" t="b">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7275663295609713</v>
+        <v>0.7216673762260467</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7409184684193753</v>
+        <v>0.7618607525791475</v>
       </c>
     </row>
     <row r="117">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:49</t>
+          <t>2026-05-28 12:39:32</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -27350,17 +27350,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-05-27 16:31:59</t>
+          <t>2026-05-28 12:39:38</t>
         </is>
       </c>
       <c r="D118" t="b">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7477534113754684</v>
+        <v>0.7452761848234843</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7566057902652451</v>
+        <v>0.7772355994200966</v>
       </c>
     </row>
     <row r="119">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:13</t>
+          <t>2026-05-28 12:39:55</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -27402,17 +27402,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:24</t>
+          <t>2026-05-28 12:40:08</t>
         </is>
       </c>
       <c r="D120" t="b">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6956973562246178</v>
+        <v>0.695694984344375</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6908490963398666</v>
+        <v>0.7075509174749333</v>
       </c>
     </row>
     <row r="121">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:32</t>
+          <t>2026-05-28 12:40:20</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -27454,17 +27454,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:41</t>
+          <t>2026-05-28 12:40:30</t>
         </is>
       </c>
       <c r="D122" t="b">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7154328652707029</v>
+        <v>0.7158439303628452</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7060062204700163</v>
+        <v>0.7224237113213305</v>
       </c>
     </row>
     <row r="123">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:48</t>
+          <t>2026-05-28 12:40:42</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -27506,14 +27506,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-05-27 16:32:54</t>
+          <t>2026-05-28 12:40:52</t>
         </is>
       </c>
       <c r="D124" t="b">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9682292912672785</v>
+        <v>0.9983676297386583</v>
       </c>
       <c r="F124" t="n">
         <v>0.9974632574897072</v>
@@ -27532,7 +27532,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:02</t>
+          <t>2026-05-28 12:41:04</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:08</t>
+          <t>2026-05-28 12:41:12</t>
         </is>
       </c>
       <c r="D126" t="b">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:15</t>
+          <t>2026-05-28 12:41:22</t>
         </is>
       </c>
       <c r="D127" t="b">
@@ -27610,14 +27610,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:21</t>
+          <t>2026-05-28 12:41:29</t>
         </is>
       </c>
       <c r="D128" t="b">
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>1.00311209767333</v>
+        <v>1.033845692266929</v>
       </c>
       <c r="F128" t="n">
         <v>1.037117535362593</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:29</t>
+          <t>2026-05-28 12:41:39</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -27662,7 +27662,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:34</t>
+          <t>2026-05-28 12:41:48</t>
         </is>
       </c>
       <c r="D130" t="b">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:42</t>
+          <t>2026-05-28 12:42:00</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -27714,14 +27714,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:48</t>
+          <t>2026-05-28 12:42:09</t>
         </is>
       </c>
       <c r="D132" t="b">
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>1.221970523745653</v>
+        <v>1.256510542780482</v>
       </c>
       <c r="F132" t="n">
         <v>1.257826861978685</v>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-05-27 16:33:56</t>
+          <t>2026-05-28 12:42:20</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:02</t>
+          <t>2026-05-28 12:42:27</t>
         </is>
       </c>
       <c r="D134" t="b">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:10</t>
+          <t>2026-05-28 12:42:38</t>
         </is>
       </c>
       <c r="D135" t="b">
@@ -27818,7 +27818,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:15</t>
+          <t>2026-05-28 12:42:45</t>
         </is>
       </c>
       <c r="D136" t="b">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:23</t>
+          <t>2026-05-28 12:42:55</t>
         </is>
       </c>
       <c r="D137" t="b">
@@ -27870,14 +27870,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:29</t>
+          <t>2026-05-28 12:43:04</t>
         </is>
       </c>
       <c r="D138" t="b">
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>1.279481143408129</v>
+        <v>1.317209476166313</v>
       </c>
       <c r="F138" t="n">
         <v>1.309163850811504</v>
@@ -27896,7 +27896,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:37</t>
+          <t>2026-05-28 12:43:15</t>
         </is>
       </c>
       <c r="D139" t="b">
